--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>В пути</t>
+          <t>ACCEPTANCE_AT_STORAGE_WAREHOUSE</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>

--- a/supplies/130117451-1.xlsx
+++ b/supplies/130117451-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
